--- a/TABELA DE PRODUTOS_TOBRAS.xlsx
+++ b/TABELA DE PRODUTOS_TOBRAS.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Tobras\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vinic\OneDrive\Área de Trabalho\Ressarcimento-CAT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A55E31F4-BFAA-482C-880D-F5D47D2858EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFC0BB2D-9708-4C47-922A-4F916F0C228C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="36525" yWindow="1590" windowWidth="27060" windowHeight="14940" xr2:uid="{A72C5968-4913-42ED-B3F0-DC6DF1BFD5B6}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{A72C5968-4913-42ED-B3F0-DC6DF1BFD5B6}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$C$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$C$23</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="53">
   <si>
     <t>item_cProd</t>
   </si>
@@ -105,12 +105,6 @@
   </si>
   <si>
     <t>OLEO DIESEL B S10   ADITIVADO ONU 1202 - CLASSE 3 - RISCO 30</t>
-  </si>
-  <si>
-    <t>100301</t>
-  </si>
-  <si>
-    <t>ETANOL ANIDRO COM CORANTE ONU 1170 - CLASSE 3 - RISCO 33</t>
   </si>
   <si>
     <t>100302</t>
@@ -639,17 +633,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A81E30D2-AFE2-46B5-A088-4E4CE37770FE}">
-  <dimension ref="A1:D24"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:D23"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19" style="3" customWidth="1"/>
-    <col min="2" max="2" width="63.5703125" style="3" customWidth="1"/>
-    <col min="3" max="3" width="18.140625" style="3" customWidth="1"/>
-    <col min="4" max="4" width="17.140625" style="3" customWidth="1"/>
-    <col min="5" max="16384" width="9.140625" style="3"/>
+    <col min="2" max="2" width="63.5546875" style="3" customWidth="1"/>
+    <col min="3" max="3" width="18.109375" style="3" customWidth="1"/>
+    <col min="4" max="4" width="17.109375" style="3" customWidth="1"/>
+    <col min="5" max="16384" width="9.109375" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -657,13 +651,13 @@
         <v>1</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>2</v>
       </c>
@@ -671,13 +665,13 @@
         <v>3</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>4</v>
       </c>
@@ -685,13 +679,13 @@
         <v>5</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>6</v>
       </c>
@@ -699,13 +693,13 @@
         <v>7</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>8</v>
       </c>
@@ -713,13 +707,13 @@
         <v>9</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>10</v>
       </c>
@@ -727,13 +721,13 @@
         <v>11</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>12</v>
       </c>
@@ -741,13 +735,13 @@
         <v>13</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>14</v>
       </c>
@@ -755,13 +749,13 @@
         <v>15</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>16</v>
       </c>
@@ -769,13 +763,13 @@
         <v>17</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>18</v>
       </c>
@@ -783,13 +777,13 @@
         <v>19</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
         <v>20</v>
       </c>
@@ -797,13 +791,13 @@
         <v>21</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
         <v>22</v>
       </c>
@@ -811,55 +805,55 @@
         <v>23</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
         <v>24</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C13" s="6" t="s">
-        <v>50</v>
+      <c r="C13" s="7" t="s">
+        <v>45</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A14" s="3">
+        <v>100502</v>
+      </c>
+      <c r="B14" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="C14" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A15" s="3" t="s">
         <v>27</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="3">
-        <v>100502</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C15" s="7" t="s">
-        <v>48</v>
+      <c r="C15" s="4" t="s">
+        <v>46</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
         <v>29</v>
       </c>
@@ -867,13 +861,13 @@
         <v>30</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
         <v>31</v>
       </c>
@@ -881,13 +875,13 @@
         <v>32</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
         <v>33</v>
       </c>
@@ -895,13 +889,13 @@
         <v>34</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
         <v>35</v>
       </c>
@@ -909,13 +903,13 @@
         <v>36</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
         <v>37</v>
       </c>
@@ -923,13 +917,13 @@
         <v>38</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
         <v>39</v>
       </c>
@@ -937,13 +931,13 @@
         <v>40</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
         <v>41</v>
       </c>
@@ -951,13 +945,13 @@
         <v>42</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
         <v>43</v>
       </c>
@@ -965,28 +959,14 @@
         <v>44</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C24" xr:uid="{A81E30D2-AFE2-46B5-A088-4E4CE37770FE}"/>
+  <autoFilter ref="A1:C23" xr:uid="{A81E30D2-AFE2-46B5-A088-4E4CE37770FE}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
--- a/TABELA DE PRODUTOS_TOBRAS.xlsx
+++ b/TABELA DE PRODUTOS_TOBRAS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vinic\OneDrive\Área de Trabalho\Ressarcimento-CAT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFC0BB2D-9708-4C47-922A-4F916F0C228C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9B529BE-23CD-4C7C-83B8-3BDA9666A0CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{A72C5968-4913-42ED-B3F0-DC6DF1BFD5B6}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$C$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$C$5</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="18">
   <si>
     <t>item_cProd</t>
   </si>
@@ -53,127 +53,22 @@
     <t>GASOLINA A COMUM ONU 1203 - CLASSE 3 - RISCO 33</t>
   </si>
   <si>
-    <t>100102</t>
-  </si>
-  <si>
-    <t>GASOLINA C COMUM ONU 3475 - CLASSE 3 - RISCO 33</t>
-  </si>
-  <si>
-    <t>100103</t>
-  </si>
-  <si>
-    <t>GASOLINA C ADITIVADA ONU 3475 - CLASSE 3 - RISCO 33</t>
-  </si>
-  <si>
-    <t>100202</t>
-  </si>
-  <si>
-    <t>BIODIESEL B100 ONU 1202 - CLASSE 3 - RISCO 30</t>
-  </si>
-  <si>
     <t>100203</t>
   </si>
   <si>
     <t>OLEO DIESEL A S500   COMUM ONU 1202 - CLASSE 3 - RISCO 30</t>
   </si>
   <si>
-    <t>100204</t>
-  </si>
-  <si>
-    <t>OLEO DIESEL B S500   COMUM ONU 1202 - CLASSE 3 - RISCO 30</t>
-  </si>
-  <si>
-    <t>100205</t>
-  </si>
-  <si>
-    <t>OLEO DIESEL B S500   ADITIVADO ONU 1202 - CLASSE 3 - RISCO 30</t>
-  </si>
-  <si>
     <t>100206</t>
   </si>
   <si>
     <t>OLEO DIESEL A S10 ONU 1202 - CLASSE 3 - RISCO 30</t>
   </si>
   <si>
-    <t>100207</t>
-  </si>
-  <si>
-    <t>OLEO DIESEL B S10   COMUM ONU 1202 - CLASSE 3 - RISCO 30</t>
-  </si>
-  <si>
-    <t>100208</t>
-  </si>
-  <si>
-    <t>OLEO DIESEL B S10   ADITIVADO ONU 1202 - CLASSE 3 - RISCO 30</t>
-  </si>
-  <si>
     <t>100302</t>
   </si>
   <si>
     <t>ETANOL HIDRATADO COMUM ONU 1170 - CLASSE 3 - RISCO 33</t>
-  </si>
-  <si>
-    <t>100501</t>
-  </si>
-  <si>
-    <t>ADITIVO GASOLINA</t>
-  </si>
-  <si>
-    <t>ADITIVO DIESEL</t>
-  </si>
-  <si>
-    <t>100640</t>
-  </si>
-  <si>
-    <t>TERRANA DIESEL POWER CI-4 15W40 - CX 12x1 CX 12x1</t>
-  </si>
-  <si>
-    <t>100641</t>
-  </si>
-  <si>
-    <t>TERRANA DIESEL SUPER CH-4 15W40 - CX 12x1 CX 12x1</t>
-  </si>
-  <si>
-    <t>100642</t>
-  </si>
-  <si>
-    <t>TERRANA HYDRA SUPER 68 - BB 20 BB 20</t>
-  </si>
-  <si>
-    <t>100643</t>
-  </si>
-  <si>
-    <t>TERRANA PLUS SL 15W40 - CX 12x1 CX 12x1</t>
-  </si>
-  <si>
-    <t>100644</t>
-  </si>
-  <si>
-    <t>TERRANA DIESEL SUPER CH-4 15W40 - BB 20 BB 20</t>
-  </si>
-  <si>
-    <t>100645</t>
-  </si>
-  <si>
-    <t>TERRANA HYDRA POWER HLP 68 - BB 20 BB 20</t>
-  </si>
-  <si>
-    <t>100646</t>
-  </si>
-  <si>
-    <t>TERRANA MASTER SN 5W30 - CX 12x1 CX 12x1</t>
-  </si>
-  <si>
-    <t>100647</t>
-  </si>
-  <si>
-    <t>TERRANA SUPER SL 20W50 - CX 12x1 CX 12x1</t>
-  </si>
-  <si>
-    <t>100648</t>
-  </si>
-  <si>
-    <t>TERRANA DIESEL POWER CI-4 15W40 BB 20</t>
   </si>
   <si>
     <t>GAC</t>
@@ -231,7 +126,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -247,12 +142,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF001E50"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -283,7 +172,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -295,7 +184,6 @@
     <xf numFmtId="164" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -633,7 +521,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A81E30D2-AFE2-46B5-A088-4E4CE37770FE}">
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19" style="3" customWidth="1"/>
@@ -651,10 +539,10 @@
         <v>1</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>50</v>
+        <v>12</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
@@ -665,10 +553,10 @@
         <v>3</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>51</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
@@ -679,10 +567,10 @@
         <v>5</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>45</v>
+        <v>11</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>51</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
@@ -693,10 +581,10 @@
         <v>7</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>45</v>
+        <v>14</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>51</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
@@ -706,267 +594,15 @@
       <c r="B5" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="7" t="s">
-        <v>46</v>
+      <c r="C5" s="6" t="s">
+        <v>13</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9" s="3" t="s">
         <v>17</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A12" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A13" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A14" s="3">
-        <v>100502</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A15" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A16" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A17" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A18" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A19" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A20" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A21" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A22" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A23" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>52</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C23" xr:uid="{A81E30D2-AFE2-46B5-A088-4E4CE37770FE}"/>
+  <autoFilter ref="A1:C5" xr:uid="{A81E30D2-AFE2-46B5-A088-4E4CE37770FE}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>